--- a/sources/yoshimitsu_step4.xlsx
+++ b/sources/yoshimitsu_step4.xlsx
@@ -696,6 +696,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
@@ -738,6 +743,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
@@ -778,6 +788,11 @@
       <c r="L8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -6778,6 +6793,11 @@
           <t>hmmhhLm[!][!]!</t>
         </is>
       </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
@@ -6805,6 +6825,11 @@
           <t>hmmhmmmm[!]!</t>
         </is>
       </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
@@ -6832,6 +6857,11 @@
           <t>hhmhhLm[!][!]!</t>
         </is>
       </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
@@ -6859,6 +6889,11 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
@@ -6886,6 +6921,11 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
@@ -6913,6 +6953,11 @@
           <t>hhmh!</t>
         </is>
       </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
@@ -6938,6 +6983,11 @@
       <c r="J140" t="inlineStr">
         <is>
           <t>hhmh!</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">

--- a/sources/yoshimitsu_step4.xlsx
+++ b/sources/yoshimitsu_step4.xlsx
@@ -2675,6 +2675,11 @@
           <t>– 1+4</t>
         </is>
       </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2+3</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>– Soul Siphon</t>
@@ -2722,6 +2727,11 @@
           <t>– F+1+4</t>
         </is>
       </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>F+2+3</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>– Possession</t>
@@ -3809,6 +3819,11 @@
           <t>– f</t>
         </is>
       </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>– Vacuum Dance</t>
@@ -4044,6 +4059,11 @@
           <t>– 1+4</t>
         </is>
       </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2+3</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>– Soul Siphon</t>
@@ -4091,6 +4111,11 @@
           <t>– F+1+4</t>
         </is>
       </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>F+2+3</t>
+        </is>
+      </c>
       <c r="C77" t="inlineStr">
         <is>
           <t>– Possession</t>
@@ -4507,6 +4532,11 @@
       <c r="A86" t="inlineStr">
         <is>
           <t>– f</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>b</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5515,6 +5545,11 @@
           <t>– u/b</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>u; u/f</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>– Jumping Flea</t>
@@ -5570,6 +5605,11 @@
       <c r="A108" t="inlineStr">
         <is>
           <t>– f,f</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>b,b</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
